--- a/data/trans_orig/Q5419_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q5419_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de usar medios de transporte en 2023</t>
+          <t>Población según si es capaz de usar medios de transporte en 2023 (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21929</t>
+          <t>22398</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37421</t>
+          <t>38117</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>68291</t>
+          <t>69395</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>91250</t>
+          <t>91757</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>94480</t>
+          <t>94483</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>122444</t>
+          <t>123370</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,08%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3229</t>
+          <t>3365</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11857</t>
+          <t>12153</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21018</t>
+          <t>20353</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36381</t>
+          <t>36506</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26102</t>
+          <t>26393</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43571</t>
+          <t>43771</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9220</t>
+          <t>10185</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22456</t>
+          <t>22542</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>43546</t>
+          <t>44440</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>64148</t>
+          <t>63004</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>57558</t>
+          <t>56735</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>81123</t>
+          <t>80270</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,46%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11818</t>
+          <t>11309</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23987</t>
+          <t>23741</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44204</t>
+          <t>44185</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63998</t>
+          <t>63958</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>58956</t>
+          <t>60462</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>83838</t>
+          <t>84205</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,98%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>188676</t>
+          <t>189243</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>212358</t>
+          <t>210103</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>78,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>269050</t>
+          <t>270012</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>300269</t>
+          <t>301159</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>466090</t>
+          <t>466854</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>505612</t>
+          <t>505511</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,75%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>65,89%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11545</t>
+          <t>10531</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2567</t>
+          <t>2226</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17601</t>
+          <t>17311</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,17 +1477,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>14249</t>
+          <t>14248</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6060</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22824</t>
+          <t>22891</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7201</t>
+          <t>8071</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>283</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>6649</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11424</t>
+          <t>11127</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3474</t>
+          <t>3586</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12353</t>
+          <t>12160</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2159</t>
+          <t>2241</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18579</t>
+          <t>18478</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6065</t>
+          <t>5635</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>25835</t>
+          <t>24722</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6822</t>
+          <t>6438</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17366</t>
+          <t>16688</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5079</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33108</t>
+          <t>33560</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10528</t>
+          <t>10869</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41502</t>
+          <t>41324</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>237840</t>
+          <t>237795</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>253204</t>
+          <t>253547</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>385700</t>
+          <t>385558</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>443839</t>
+          <t>443241</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>636721</t>
+          <t>636200</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>703450</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,11%</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7369</t>
+          <t>6242</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3110</t>
+          <t>3028</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6878</t>
+          <t>7133</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>594</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6471</t>
+          <t>5681</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6091</t>
+          <t>5983</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2768</t>
+          <t>3226</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1543</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7389</t>
+          <t>7709</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>1705</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8919</t>
+          <t>8935</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4283</t>
+          <t>4026</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1249</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>5729</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>1734</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7893</t>
+          <t>7475</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>94625</t>
+          <t>93888</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>102618</t>
+          <t>102587</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>59846</t>
+          <t>60137</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>67395</t>
+          <t>67339</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>158070</t>
+          <t>157158</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>168869</t>
+          <t>168643</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,65%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28508</t>
+          <t>28065</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>46400</t>
+          <t>46571</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43351</t>
+          <t>49916</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>116485</t>
+          <t>115965</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>83491</t>
+          <t>82485</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>149261</t>
+          <t>147732</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7060</t>
+          <t>7308</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18656</t>
+          <t>18325</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>15749</t>
+          <t>16617</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>42553</t>
+          <t>42409</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>26822</t>
+          <t>27581</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>53350</t>
+          <t>55421</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16427</t>
+          <t>16375</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>31649</t>
+          <t>31544</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>32909</t>
+          <t>34074</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>86922</t>
+          <t>87041</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>59461</t>
+          <t>59353</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>107232</t>
+          <t>108233</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22221</t>
+          <t>22564</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>37892</t>
+          <t>38671</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>36409</t>
+          <t>38893</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>95624</t>
+          <t>96046</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>67684</t>
+          <t>65220</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>122665</t>
+          <t>122511</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>529276</t>
+          <t>529926</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>559734</t>
+          <t>559430</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>697028</t>
+          <t>696149</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>889809</t>
+          <t>876497</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1256846</t>
+          <t>1256893</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1427259</t>
+          <t>1428516</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,41%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5419_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q5419_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>29231</t>
+          <t>31093</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22398</t>
+          <t>23335</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>40805</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>79209</t>
+          <t>85272</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>69395</t>
+          <t>73637</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>91757</t>
+          <t>97556</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>108441</t>
+          <t>116365</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>94483</t>
+          <t>100017</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>123370</t>
+          <t>130989</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,86%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6595</t>
+          <t>6699</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3365</t>
+          <t>3268</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12153</t>
+          <t>12126</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27427</t>
+          <t>29181</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20353</t>
+          <t>21446</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36506</t>
+          <t>38278</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>34022</t>
+          <t>35880</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26393</t>
+          <t>27482</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43771</t>
+          <t>46911</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15563</t>
+          <t>16506</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10185</t>
+          <t>10574</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22542</t>
+          <t>23566</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>53010</t>
+          <t>56600</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>44440</t>
+          <t>46814</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>63004</t>
+          <t>68581</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,27 +1021,27 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>68574</t>
+          <t>73105</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>56735</t>
+          <t>60497</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>80270</t>
+          <t>86365</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17090</t>
+          <t>18111</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11309</t>
+          <t>12076</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23741</t>
+          <t>25522</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>53958</t>
+          <t>58646</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44185</t>
+          <t>48033</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63958</t>
+          <t>70339</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>71048</t>
+          <t>76757</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>60462</t>
+          <t>65422</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>84205</t>
+          <t>90975</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,02%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>199906</t>
+          <t>216757</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>189243</t>
+          <t>204036</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>210103</t>
+          <t>228314</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>285228</t>
+          <t>306920</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>270012</t>
+          <t>291292</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>301159</t>
+          <t>325237</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>485133</t>
+          <t>523678</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>466854</t>
+          <t>501765</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>505511</t>
+          <t>545713</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>63,42%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>66,08%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>268386</t>
+          <t>289166</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>268386</t>
+          <t>289166</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>268386</t>
+          <t>289166</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>498833</t>
+          <t>536619</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>498833</t>
+          <t>536619</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>498833</t>
+          <t>536619</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>767218</t>
+          <t>825785</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>767218</t>
+          <t>825785</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>767218</t>
+          <t>825785</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5950</t>
+          <t>6031</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>2976</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10531</t>
+          <t>10534</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>9518</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2226</t>
+          <t>5855</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17311</t>
+          <t>15259</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>14248</t>
+          <t>15549</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>10369</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22891</t>
+          <t>22574</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3259</t>
+          <t>3323</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>1161</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8071</t>
+          <t>7976</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2933</t>
+          <t>3567</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>1444</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6649</t>
+          <t>7180</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>6193</t>
+          <t>6890</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11127</t>
+          <t>11664</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7000</t>
+          <t>7700</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3586</t>
+          <t>3823</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12160</t>
+          <t>14042</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8651</t>
+          <t>10352</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2241</t>
+          <t>6497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18478</t>
+          <t>16496</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>15651</t>
+          <t>18052</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5635</t>
+          <t>12159</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>24722</t>
+          <t>25968</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10940</t>
+          <t>11173</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6438</t>
+          <t>6527</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16688</t>
+          <t>18129</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>15971</t>
+          <t>18177</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5070</t>
+          <t>13123</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33560</t>
+          <t>25235</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>26911</t>
+          <t>29351</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10869</t>
+          <t>22606</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41324</t>
+          <t>38282</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>246108</t>
+          <t>275597</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>237795</t>
+          <t>266743</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>253547</t>
+          <t>283266</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>419885</t>
+          <t>236031</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>385558</t>
+          <t>226448</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>443241</t>
+          <t>244005</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>665994</t>
+          <t>511628</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>636200</t>
+          <t>498134</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>700617</t>
+          <t>522011</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>89,77%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>455739</t>
+          <t>277646</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>455739</t>
+          <t>277646</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>455739</t>
+          <t>277646</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>728996</t>
+          <t>581471</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>728996</t>
+          <t>581471</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>728996</t>
+          <t>581471</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>2125</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2099,92 +2099,92 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6242</t>
+          <t>7785</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6,55%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3328</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>4,02%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>2778</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>8389</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
           <t>1,38%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>5,95%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>601</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3028</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>4,25%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>2050</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>7133</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2098</t>
+          <t>2226</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>620</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5681</t>
+          <t>6967</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2098</t>
+          <t>2226</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>614</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5983</t>
+          <t>5899</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>553</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2325,12 +2325,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3226</t>
+          <t>2824</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3637</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1381</t>
+          <t>1376</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7709</t>
+          <t>8163</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>4175</t>
+          <t>4399</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1705</t>
+          <t>1861</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8935</t>
+          <t>8840</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1164</t>
+          <t>1168</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2438,12 +2438,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4026</t>
+          <t>3638</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2782</t>
+          <t>3784</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5729</t>
+          <t>7195</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>4952</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1734</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7475</t>
+          <t>9208</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>99737</t>
+          <t>112810</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>93888</t>
+          <t>106515</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>102587</t>
+          <t>116153</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>64305</t>
+          <t>74572</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>60137</t>
+          <t>69877</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>67339</t>
+          <t>77996</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>164042</t>
+          <t>187382</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>157158</t>
+          <t>180007</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>168643</t>
+          <t>192350</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,35%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>36631</t>
+          <t>39249</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28065</t>
+          <t>30025</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>46571</t>
+          <t>49948</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>88109</t>
+          <t>95443</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>49916</t>
+          <t>83571</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>115965</t>
+          <t>109276</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>124739</t>
+          <t>134692</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>82485</t>
+          <t>118612</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>147732</t>
+          <t>151906</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>11952</t>
+          <t>12248</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7308</t>
+          <t>7300</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18325</t>
+          <t>19285</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>30360</t>
+          <t>32748</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>16617</t>
+          <t>25072</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>42409</t>
+          <t>41996</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>42312</t>
+          <t>44996</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>27581</t>
+          <t>35537</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>55421</t>
+          <t>56182</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>23102</t>
+          <t>24758</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16375</t>
+          <t>17711</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>31544</t>
+          <t>33769</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>65298</t>
+          <t>70798</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>34074</t>
+          <t>59402</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>87041</t>
+          <t>83126</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>88400</t>
+          <t>95557</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>59353</t>
+          <t>81253</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>108233</t>
+          <t>110421</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>29194</t>
+          <t>30452</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22564</t>
+          <t>21846</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>38671</t>
+          <t>40166</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>72711</t>
+          <t>80608</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>38893</t>
+          <t>69690</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>96046</t>
+          <t>92923</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>101905</t>
+          <t>111060</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>65220</t>
+          <t>96452</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>122511</t>
+          <t>126890</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>545751</t>
+          <t>605165</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>529926</t>
+          <t>589599</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>559430</t>
+          <t>620601</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>769419</t>
+          <t>617523</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>696149</t>
+          <t>597462</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>876497</t>
+          <t>638428</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1315169</t>
+          <t>1222688</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1256893</t>
+          <t>1197730</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1428516</t>
+          <t>1249807</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>77,68%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>646628</t>
+          <t>711872</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>646628</t>
+          <t>711872</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>646628</t>
+          <t>711872</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1025897</t>
+          <t>897120</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1025897</t>
+          <t>897120</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1025897</t>
+          <t>897120</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1672525</t>
+          <t>1608992</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1672525</t>
+          <t>1608992</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1672525</t>
+          <t>1608992</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
